--- a/docs/harness/wirelist/A-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/A-engine-wirelist.xlsx
@@ -1218,12 +1218,12 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>DRB102 1 = section A c48 'Switched 12V - INJECTOR power feed, fuse LOGIC INJ'</t>
+          <t>DRB102 1 = section A c48 'Switched 12V - INJECTOR power feed, fuse LOGIC INJ'; splice sp_inj_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_inj_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG3" s="38" t="inlineStr"/>
@@ -1329,12 +1329,12 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>DRB102 2 = section A c49 'Switched 12V - COP / ignition coil power feed, fus'</t>
+          <t>DRB102 2 = section A c49 'Switched 12V - COP / ignition coil power feed, fus'; splice sp_cop_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_cop_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG4" s="54" t="inlineStr"/>
@@ -2705,12 +2705,12 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>DRB102 20 = section A c5 'Switched 12V to engine sensors'</t>
+          <t>DRB102 20 = section A c5 'Switched 12V to engine sensors'; splice sp_sw12_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_sw12_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG16" s="54" t="inlineStr"/>
@@ -2771,8 +2771,10 @@
           <t>Flex fuel sensor (fuel return line)</t>
         </is>
       </c>
-      <c r="N17" s="28" t="n">
-        <v>3</v>
+      <c r="N17" s="28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="O17" s="29" t="inlineStr">
         <is>
@@ -2820,12 +2822,12 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>DRB102 21 = section A c9 'ECU-A A31'; device ref Flex fuel — Continental generic 3-pin pin 3 'Vout sensor output'</t>
+          <t>DRB102 21 = section A c9 'ECU-A A31'; device ref Flex fuel — Continental generic 3-pin pin C 'Vout sensor output'</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: flex pins are drawn without the device's pin letters (reference: A, B, C)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG17" s="38" t="inlineStr"/>
@@ -3393,12 +3395,12 @@
       <c r="AD22" s="54" t="inlineStr"/>
       <c r="AE22" s="54" t="inlineStr">
         <is>
-          <t>DRB102 26 = section A c3 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 26 = section A c3 'Gnd Out to engine sensors (sensor GND bus plug bus'; splice sp_gndout_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF22" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG22" s="54" t="inlineStr"/>
@@ -3732,12 +3734,12 @@
       <c r="AD25" s="38" t="inlineStr"/>
       <c r="AE25" s="38" t="inlineStr">
         <is>
-          <t>DRB102 29 = section A c44 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 29 = section A c44 'Gnd Out to engine sensors (sensor GND bus plug bus'; splice sp_gndout_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF25" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_eng2 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG25" s="38" t="inlineStr"/>
@@ -5869,10 +5871,14 @@
       <c r="AB44" s="53" t="inlineStr"/>
       <c r="AC44" s="54" t="inlineStr"/>
       <c r="AD44" s="54" t="inlineStr"/>
-      <c r="AE44" s="54" t="inlineStr"/>
+      <c r="AE44" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_sw12_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF44" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_sw12_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG44" s="54" t="inlineStr"/>
@@ -5976,10 +5982,14 @@
       <c r="AB45" s="37" t="inlineStr"/>
       <c r="AC45" s="38" t="inlineStr"/>
       <c r="AD45" s="38" t="inlineStr"/>
-      <c r="AE45" s="38" t="inlineStr"/>
+      <c r="AE45" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_cop_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF45" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_cop_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG45" s="38" t="inlineStr"/>
@@ -6083,10 +6093,14 @@
       <c r="AB46" s="53" t="inlineStr"/>
       <c r="AC46" s="54" t="inlineStr"/>
       <c r="AD46" s="54" t="inlineStr"/>
-      <c r="AE46" s="54" t="inlineStr"/>
+      <c r="AE46" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_chassis_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF46" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_chassis_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG46" s="54" t="inlineStr"/>
@@ -6190,10 +6204,14 @@
       <c r="AB47" s="37" t="inlineStr"/>
       <c r="AC47" s="38" t="inlineStr"/>
       <c r="AD47" s="38" t="inlineStr"/>
-      <c r="AE47" s="38" t="inlineStr"/>
+      <c r="AE47" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_cop_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF47" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_cop_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG47" s="38" t="inlineStr"/>
@@ -6297,10 +6315,14 @@
       <c r="AB48" s="53" t="inlineStr"/>
       <c r="AC48" s="54" t="inlineStr"/>
       <c r="AD48" s="54" t="inlineStr"/>
-      <c r="AE48" s="54" t="inlineStr"/>
+      <c r="AE48" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_chassis_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF48" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_chassis_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG48" s="54" t="inlineStr"/>
@@ -6404,10 +6426,14 @@
       <c r="AB49" s="37" t="inlineStr"/>
       <c r="AC49" s="38" t="inlineStr"/>
       <c r="AD49" s="38" t="inlineStr"/>
-      <c r="AE49" s="38" t="inlineStr"/>
+      <c r="AE49" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_cop_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF49" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_cop_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG49" s="38" t="inlineStr"/>
@@ -6511,10 +6537,14 @@
       <c r="AB50" s="53" t="inlineStr"/>
       <c r="AC50" s="54" t="inlineStr"/>
       <c r="AD50" s="54" t="inlineStr"/>
-      <c r="AE50" s="54" t="inlineStr"/>
+      <c r="AE50" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_chassis_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF50" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_chassis_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG50" s="54" t="inlineStr"/>
@@ -6618,10 +6648,14 @@
       <c r="AB51" s="37" t="inlineStr"/>
       <c r="AC51" s="38" t="inlineStr"/>
       <c r="AD51" s="38" t="inlineStr"/>
-      <c r="AE51" s="38" t="inlineStr"/>
+      <c r="AE51" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_cop_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF51" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_cop_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG51" s="38" t="inlineStr"/>
@@ -6725,10 +6759,14 @@
       <c r="AB52" s="53" t="inlineStr"/>
       <c r="AC52" s="54" t="inlineStr"/>
       <c r="AD52" s="54" t="inlineStr"/>
-      <c r="AE52" s="54" t="inlineStr"/>
+      <c r="AE52" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_chassis_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF52" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_chassis_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG52" s="54" t="inlineStr"/>
@@ -6836,10 +6874,14 @@
       <c r="AB53" s="37" t="inlineStr"/>
       <c r="AC53" s="38" t="inlineStr"/>
       <c r="AD53" s="38" t="inlineStr"/>
-      <c r="AE53" s="38" t="inlineStr"/>
+      <c r="AE53" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_gndout_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF53" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG53" s="38" t="inlineStr"/>
@@ -6947,10 +6989,14 @@
       <c r="AB54" s="53" t="inlineStr"/>
       <c r="AC54" s="54" t="inlineStr"/>
       <c r="AD54" s="54" t="inlineStr"/>
-      <c r="AE54" s="54" t="inlineStr"/>
+      <c r="AE54" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_gndout_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF54" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG54" s="54" t="inlineStr"/>
@@ -6987,8 +7033,10 @@
           <t>Flex fuel sensor (fuel return line)</t>
         </is>
       </c>
-      <c r="H55" s="25" t="n">
-        <v>1</v>
+      <c r="H55" s="25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="I55" s="26" t="inlineStr">
         <is>
@@ -7060,12 +7108,12 @@
       <c r="AD55" s="38" t="inlineStr"/>
       <c r="AE55" s="38" t="inlineStr">
         <is>
-          <t>device ref Flex fuel — Continental generic 3-pin pin 1 'VCC 12VDC'</t>
+          <t>device ref Flex fuel — Continental generic 3-pin pin A 'VCC 12VDC'; splice sp_sw12_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF55" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: flex pins are drawn without the device's pin letters (reference: A, B, C); splice sp_sw12_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG55" s="38" t="inlineStr"/>
@@ -7102,8 +7150,10 @@
           <t>Flex fuel sensor (fuel return line)</t>
         </is>
       </c>
-      <c r="H56" s="41" t="n">
-        <v>2</v>
+      <c r="H56" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="I56" s="42" t="inlineStr">
         <is>
@@ -7175,12 +7225,12 @@
       <c r="AD56" s="54" t="inlineStr"/>
       <c r="AE56" s="54" t="inlineStr">
         <is>
-          <t>device ref Flex fuel — Continental generic 3-pin pin 2 'GND signal ground'</t>
+          <t>device ref Flex fuel — Continental generic 3-pin pin B 'GND signal ground'; splice sp_gndout_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF56" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: flex pins are drawn without the device's pin letters (reference: A, B, C); splice sp_gndout_eng2 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG56" s="54" t="inlineStr"/>
@@ -7288,10 +7338,14 @@
       <c r="AB57" s="37" t="inlineStr"/>
       <c r="AC57" s="38" t="inlineStr"/>
       <c r="AD57" s="38" t="inlineStr"/>
-      <c r="AE57" s="38" t="inlineStr"/>
+      <c r="AE57" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_gndout_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF57" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG57" s="38" t="inlineStr"/>
@@ -7395,10 +7449,14 @@
       <c r="AB58" s="53" t="inlineStr"/>
       <c r="AC58" s="54" t="inlineStr"/>
       <c r="AD58" s="54" t="inlineStr"/>
-      <c r="AE58" s="54" t="inlineStr"/>
+      <c r="AE58" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_inj_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF58" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_inj_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG58" s="54" t="inlineStr"/>
@@ -7502,10 +7560,14 @@
       <c r="AB59" s="37" t="inlineStr"/>
       <c r="AC59" s="38" t="inlineStr"/>
       <c r="AD59" s="38" t="inlineStr"/>
-      <c r="AE59" s="38" t="inlineStr"/>
+      <c r="AE59" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_inj_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF59" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_inj_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG59" s="38" t="inlineStr"/>
@@ -7609,10 +7671,14 @@
       <c r="AB60" s="53" t="inlineStr"/>
       <c r="AC60" s="54" t="inlineStr"/>
       <c r="AD60" s="54" t="inlineStr"/>
-      <c r="AE60" s="54" t="inlineStr"/>
+      <c r="AE60" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_inj_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF60" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_inj_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG60" s="54" t="inlineStr"/>
@@ -7716,10 +7782,14 @@
       <c r="AB61" s="37" t="inlineStr"/>
       <c r="AC61" s="38" t="inlineStr"/>
       <c r="AD61" s="38" t="inlineStr"/>
-      <c r="AE61" s="38" t="inlineStr"/>
+      <c r="AE61" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_inj_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF61" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_inj_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG61" s="38" t="inlineStr"/>
@@ -7827,12 +7897,12 @@
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan k_str 30 (10 AWG)</t>
+          <t>fuse-box plan k_str 30 (10 AWG); end starter_trigger: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end starter_trigger (Starter solenoid S (50) terminal post, spade) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG62" s="54" t="inlineStr">
@@ -7946,12 +8016,12 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>device ref MAP — Lowdoller 899005 pin 1 'low reference/ground'</t>
+          <t>device ref MAP — Lowdoller 899005 pin 1 'low reference/ground'; splice sp_gndout_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_eng2 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG63" s="38" t="inlineStr"/>
@@ -8053,10 +8123,14 @@
       <c r="AB64" s="53" t="inlineStr"/>
       <c r="AC64" s="54" t="inlineStr"/>
       <c r="AD64" s="54" t="inlineStr"/>
-      <c r="AE64" s="54" t="inlineStr"/>
+      <c r="AE64" s="54" t="inlineStr">
+        <is>
+          <t>end eng_gnd_ring: end row of the wire list (SoT); splice sp_chassis_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF64" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end eng_gnd_ring (Engine block ground stud (RADLOK engine ground, H6), M6 ring) is drawing-only: not named in the SoT; splice sp_chassis_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG64" s="54" t="inlineStr"/>
@@ -9334,7 +9408,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9464,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9520,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9576,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9632,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9688,7 @@
       </c>
       <c r="L8" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/A-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/A-engine-wirelist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$99</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG79"/>
+  <dimension ref="A1:AG99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="H3" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="26" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>DRB102 1 = section A c48 'Switched 12V - INJECTOR power feed, fuse LOGIC INJ'; splice sp_inj_eng: node of the wire list (SoT)</t>
+          <t>DRB102 2 = loom A c2 'Injector +12 V feed'; splice sp_inj_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="H4" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>DRB102 2 = section A c49 'Switched 12V - COP / ignition coil power feed, fus'; splice sp_cop_eng: node of the wire list (SoT)</t>
+          <t>DRB102 1 = loom A c1 'Coil +12 V feed'; splice sp_cop_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="H5" s="25" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>DRB102 9 = section A c24 'ECU-A A8'</t>
+          <t>DRB102 74 = loom A c74 'ECU-A A8'</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="H6" s="41" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>DRB102 10 = section A c41 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 75 = loom A c75 'Gnd crank sensor'</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="H7" s="25" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
       <c r="AD7" s="38" t="inlineStr"/>
       <c r="AE7" s="38" t="inlineStr">
         <is>
-          <t>DRB102 11 = section A c33 'Crank VR screen'</t>
+          <t>DRB102 76 = loom A c76 'Crank sensor shield'</t>
         </is>
       </c>
       <c r="AF7" s="38" t="inlineStr">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="H8" s="41" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
       <c r="AD8" s="54" t="inlineStr"/>
       <c r="AE8" s="54" t="inlineStr">
         <is>
-          <t>DRB102 12 = section A c4 '+8V Out to cam Hall'</t>
+          <t>DRB102 63 = loom A c63 '+8 V to cam sensor'</t>
         </is>
       </c>
       <c r="AF8" s="54" t="inlineStr">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="H9" s="25" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       <c r="AD9" s="38" t="inlineStr"/>
       <c r="AE9" s="38" t="inlineStr">
         <is>
-          <t>DRB102 13 = section A c29 'ECU-A A9'</t>
+          <t>DRB102 64 = loom A c64 'Cam sensor signal'</t>
         </is>
       </c>
       <c r="AF9" s="38" t="inlineStr">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="H10" s="41" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       <c r="AD10" s="54" t="inlineStr"/>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>DRB102 14 = section A c42 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 65 = loom A c65 'Gnd cam sensor'</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="H11" s="25" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>DRB102 15 = section A c34 'Cam Hall screen'</t>
+          <t>DRB102 66 = loom A c66 'Cam sensor shield'</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H12" s="41" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I12" s="42" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       <c r="AD12" s="54" t="inlineStr"/>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>DRB102 16 = section A c40 '+5V Out to engine sensors (+5 V bus plug bus_5v_bh'</t>
+          <t>DRB102 52 = loom A c52 '+5 V turbo speed'</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="H13" s="25" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       <c r="AD13" s="38" t="inlineStr"/>
       <c r="AE13" s="38" t="inlineStr">
         <is>
-          <t>DRB102 17 = section A c7 'ECU-A A30'</t>
+          <t>DRB102 53 = loom A c53 'ECU-A A30'</t>
         </is>
       </c>
       <c r="AF13" s="38" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="H14" s="41" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I14" s="42" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>DRB102 18 = section A c43 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 56 = loom A c56 'Gnd turbo speed'</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="H15" s="25" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>DRB102 19 = section A c6 'Turbo speed screen (to A7)'</t>
+          <t>DRB102 57 = loom A c57 'Turbo speed shield'</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="H16" s="41" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>DRB102 20 = section A c5 'Switched 12V to engine sensors'; splice sp_sw12_eng: node of the wire list (SoT)</t>
+          <t>DRB102 30 = loom A c30 '+12 V boost + flex'; splice sp_sw12_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="H17" s="25" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>DRB102 21 = section A c9 'ECU-A A31'; device ref Flex fuel — Continental generic 3-pin pin C 'Vout sensor output'</t>
+          <t>DRB102 31 = loom A c31 'ECU-A A31'; device ref Flex fuel — Continental generic 3-pin pin C 'Vout sensor output'</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="H18" s="41" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I18" s="42" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>DRB102 22 = section A c10 'Flex fuel screen (to A7)'</t>
+          <t>DRB102 32 = loom A c32 'Flex fuel shield'</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="H19" s="25" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>DRB102 23 = section A c2 '+5V Out to engine sensors (+5 V bus plug bus_5v_bh'</t>
+          <t>DRB102 41 = loom A c41 '+5 V throttle sensor'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="H20" s="41" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="I20" s="42" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>DRB102 24 = section A c21 'ECU-A A22'</t>
+          <t>DRB102 42 = loom A c42 'ECU-A A22'</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="H21" s="25" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>DRB102 25 = section A c22 'ECU-A A33'</t>
+          <t>DRB102 44 = loom A c44 'ECU-A A33'</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="H22" s="41" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I22" s="42" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       <c r="AD22" s="54" t="inlineStr"/>
       <c r="AE22" s="54" t="inlineStr">
         <is>
-          <t>DRB102 26 = section A c3 'Gnd Out to engine sensors (sensor GND bus plug bus'; splice sp_gndout_eng: node of the wire list (SoT)</t>
+          <t>DRB102 34 = loom A c34 'Gnd IAT/TPS/coolant'; splice sp_gndout_eng: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF22" s="54" t="inlineStr">
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="H23" s="25" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
       <c r="AD23" s="38" t="inlineStr"/>
       <c r="AE23" s="38" t="inlineStr">
         <is>
-          <t>DRB102 27 = section A c11 'ETB sensor group screen (to A7)'</t>
+          <t>DRB102 47 = loom A c47 'Throttle shield'</t>
         </is>
       </c>
       <c r="AF23" s="38" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="H24" s="41" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I24" s="42" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="54" t="inlineStr">
         <is>
-          <t>DRB102 28 = section A c39 '+5V Out to engine sensors (+5 V bus plug bus_5v_bh'; device ref MAP — Lowdoller 899005 pin 2 '5V'</t>
+          <t>DRB102 16 = loom A c16 '+5 V MAP sensor'; device ref MAP — Lowdoller 899005 pin 2 '5V'</t>
         </is>
       </c>
       <c r="AF24" s="54" t="inlineStr">
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="H25" s="25" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       <c r="AD25" s="38" t="inlineStr"/>
       <c r="AE25" s="38" t="inlineStr">
         <is>
-          <t>DRB102 29 = section A c44 'Gnd Out to engine sensors (sensor GND bus plug bus'; splice sp_gndout_eng2: node of the wire list (SoT)</t>
+          <t>DRB102 18 = loom A c18 'Gnd flex + MAP'; splice sp_gndout_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF25" s="38" t="inlineStr">
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="H26" s="41" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I26" s="42" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       <c r="AD26" s="54" t="inlineStr"/>
       <c r="AE26" s="54" t="inlineStr">
         <is>
-          <t>DRB102 30 = section A c8 'ECU-A A17'; device ref MAP — Lowdoller 899005 pin 3 'signal'</t>
+          <t>DRB102 17 = loom A c17 'ECU-A A17'; device ref MAP — Lowdoller 899005 pin 3 'signal'</t>
         </is>
       </c>
       <c r="AF26" s="54" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="H27" s="25" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AD27" s="38" t="inlineStr"/>
       <c r="AE27" s="38" t="inlineStr">
         <is>
-          <t>DRB102 31 = section A c13 'ECU-A A4'</t>
+          <t>DRB102 21 = loom A c21 'ECU-A A4'</t>
         </is>
       </c>
       <c r="AF27" s="38" t="inlineStr">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="H28" s="41" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I28" s="42" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       <c r="AD28" s="54" t="inlineStr"/>
       <c r="AE28" s="54" t="inlineStr">
         <is>
-          <t>DRB102 32 = section A c14 'ECU-A A3'</t>
+          <t>DRB102 22 = loom A c22 'ECU-A A3'</t>
         </is>
       </c>
       <c r="AF28" s="54" t="inlineStr">
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="H29" s="25" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I29" s="26" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
       <c r="AD29" s="38" t="inlineStr"/>
       <c r="AE29" s="38" t="inlineStr">
         <is>
-          <t>DRB102 33 = section A c15 'ECU-A A2'</t>
+          <t>DRB102 23 = loom A c23 'ECU-A A2'</t>
         </is>
       </c>
       <c r="AF29" s="38" t="inlineStr">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="H30" s="41" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I30" s="42" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
       <c r="AD30" s="54" t="inlineStr"/>
       <c r="AE30" s="54" t="inlineStr">
         <is>
-          <t>DRB102 34 = section A c16 'ECU-A A1'</t>
+          <t>DRB102 24 = loom A c24 'ECU-A A1'</t>
         </is>
       </c>
       <c r="AF30" s="54" t="inlineStr">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="H31" s="25" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="I31" s="26" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
       <c r="AD31" s="38" t="inlineStr"/>
       <c r="AE31" s="38" t="inlineStr">
         <is>
-          <t>DRB102 35 = section A c17 'ECU-A A13'</t>
+          <t>DRB102 9 = loom A c9 'ECU-A A13'</t>
         </is>
       </c>
       <c r="AF31" s="38" t="inlineStr">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="H32" s="41" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="I32" s="42" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
       <c r="AD32" s="54" t="inlineStr"/>
       <c r="AE32" s="54" t="inlineStr">
         <is>
-          <t>DRB102 36 = section A c18 'ECU-A A12'</t>
+          <t>DRB102 10 = loom A c10 'ECU-A A12'</t>
         </is>
       </c>
       <c r="AF32" s="54" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="H33" s="25" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="I33" s="26" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
       <c r="AD33" s="38" t="inlineStr"/>
       <c r="AE33" s="38" t="inlineStr">
         <is>
-          <t>DRB102 37 = section A c19 'ECU-A A11'</t>
+          <t>DRB102 11 = loom A c11 'ECU-A A11'</t>
         </is>
       </c>
       <c r="AF33" s="38" t="inlineStr">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="H34" s="41" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I34" s="42" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="AD34" s="54" t="inlineStr"/>
       <c r="AE34" s="54" t="inlineStr">
         <is>
-          <t>DRB102 38 = section A c20 'ECU-A A10'</t>
+          <t>DRB102 12 = loom A c12 'ECU-A A10'</t>
         </is>
       </c>
       <c r="AF34" s="54" t="inlineStr">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="H35" s="25" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="I35" s="26" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
       <c r="AD35" s="38" t="inlineStr"/>
       <c r="AE35" s="38" t="inlineStr">
         <is>
-          <t>DRB102 39 = section A c23 'ECU-A A21'</t>
+          <t>DRB102 58 = loom A c58 'ECU-A A21'</t>
         </is>
       </c>
       <c r="AF35" s="38" t="inlineStr">
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="H36" s="41" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I36" s="42" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       <c r="AD36" s="54" t="inlineStr"/>
       <c r="AE36" s="54" t="inlineStr">
         <is>
-          <t>DRB102 40 = section A c25 'ECU-A A15'</t>
+          <t>DRB102 70 = loom A c70 'ECU-A A15'</t>
         </is>
       </c>
       <c r="AF36" s="54" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="H37" s="25" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I37" s="26" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       <c r="AD37" s="38" t="inlineStr"/>
       <c r="AE37" s="38" t="inlineStr">
         <is>
-          <t>DRB102 41 = section A c26 'ECU-A A16'</t>
+          <t>DRB102 33 = loom A c33 'ECU-A A16'</t>
         </is>
       </c>
       <c r="AF37" s="38" t="inlineStr">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="H38" s="41" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="I38" s="42" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
       <c r="AD38" s="54" t="inlineStr"/>
       <c r="AE38" s="54" t="inlineStr">
         <is>
-          <t>DRB102 47 = section A c45 '+5V Out to B engine sensors via IX_B_RAIL - oil pr'</t>
+          <t>DRB102 27 = loom A c27 '+5 V oil pressure'</t>
         </is>
       </c>
       <c r="AF38" s="54" t="inlineStr">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="H39" s="25" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="I39" s="26" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       <c r="AD39" s="38" t="inlineStr"/>
       <c r="AE39" s="38" t="inlineStr">
         <is>
-          <t>DRB102 50 = section A c46 '+5V Out to B engine sensors via IX_B_RAIL - fuel p'</t>
+          <t>DRB102 13 = loom A c13 '+5 V fuel pressure'</t>
         </is>
       </c>
       <c r="AF39" s="38" t="inlineStr">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="H40" s="41" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I40" s="42" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
       <c r="AD40" s="54" t="inlineStr"/>
       <c r="AE40" s="54" t="inlineStr">
         <is>
-          <t>DRB102 51 = section A c47 '+5V Out to B engine sensors via IX_B_RAIL - coolan'</t>
+          <t>DRB102 25 = loom A c25 '+5 V coolant press'</t>
         </is>
       </c>
       <c r="AF40" s="54" t="inlineStr">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="H41" s="25" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="I41" s="26" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
       <c r="AD41" s="38" t="inlineStr"/>
       <c r="AE41" s="38" t="inlineStr">
         <is>
-          <t>DRB102 86 = section B c5 'ETB motor + (Aux 9, B18)'</t>
+          <t>DRB102 45 = loom B c45 'ECU-B B18'</t>
         </is>
       </c>
       <c r="AF41" s="38" t="inlineStr">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="H42" s="41" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="I42" s="42" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
       <c r="AD42" s="54" t="inlineStr"/>
       <c r="AE42" s="54" t="inlineStr">
         <is>
-          <t>DRB102 87 = section B c6 'ETB motor - (Aux 10, B26)'</t>
+          <t>DRB102 46 = loom B c46 'ECU-B B26'</t>
         </is>
       </c>
       <c r="AF42" s="54" t="inlineStr">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="H43" s="25" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="I43" s="26" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       <c r="AD43" s="38" t="inlineStr"/>
       <c r="AE43" s="38" t="inlineStr">
         <is>
-          <t>DRB102 88 = section B c22 'ETB motor screen (to B17)'</t>
+          <t>DRB102 50 = loom B c50 'ETB motor shield'</t>
         </is>
       </c>
       <c r="AF43" s="38" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="F65" s="25" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>cop1</t>
         </is>
       </c>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+          <t>Ignition coil cyl 1</t>
         </is>
       </c>
       <c r="H65" s="25" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J65" s="26" t="inlineStr"/>
@@ -8176,12 +8176,12 @@
       <c r="P65" s="29" t="inlineStr"/>
       <c r="Q65" s="30" t="inlineStr">
         <is>
-          <t>DRB102.45</t>
+          <t>cop1.2</t>
         </is>
       </c>
       <c r="R65" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 45)</t>
+          <t>spare (cop1 2)</t>
         </is>
       </c>
       <c r="S65" s="32" t="inlineStr"/>
@@ -8196,11 +8196,7 @@
       <c r="AB65" s="37" t="inlineStr"/>
       <c r="AC65" s="38" t="inlineStr"/>
       <c r="AD65" s="38" t="inlineStr"/>
-      <c r="AE65" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
-        </is>
-      </c>
+      <c r="AE65" s="38" t="inlineStr"/>
       <c r="AF65" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8224,20 +8220,20 @@
       </c>
       <c r="F66" s="41" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>cop2</t>
         </is>
       </c>
       <c r="G66" s="42" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+          <t>Ignition coil cyl 2</t>
         </is>
       </c>
       <c r="H66" s="41" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J66" s="42" t="inlineStr"/>
@@ -8249,12 +8245,12 @@
       <c r="P66" s="45" t="inlineStr"/>
       <c r="Q66" s="46" t="inlineStr">
         <is>
-          <t>DRB102.46</t>
+          <t>cop2.2</t>
         </is>
       </c>
       <c r="R66" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 46)</t>
+          <t>spare (cop2 2)</t>
         </is>
       </c>
       <c r="S66" s="48" t="inlineStr"/>
@@ -8269,11 +8265,7 @@
       <c r="AB66" s="53" t="inlineStr"/>
       <c r="AC66" s="54" t="inlineStr"/>
       <c r="AD66" s="54" t="inlineStr"/>
-      <c r="AE66" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
-        </is>
-      </c>
+      <c r="AE66" s="54" t="inlineStr"/>
       <c r="AF66" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8297,20 +8289,20 @@
       </c>
       <c r="F67" s="25" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>cop3</t>
         </is>
       </c>
       <c r="G67" s="26" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+          <t>Ignition coil cyl 3</t>
         </is>
       </c>
       <c r="H67" s="25" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J67" s="26" t="inlineStr"/>
@@ -8322,12 +8314,12 @@
       <c r="P67" s="29" t="inlineStr"/>
       <c r="Q67" s="30" t="inlineStr">
         <is>
-          <t>DRB102.52</t>
+          <t>cop3.2</t>
         </is>
       </c>
       <c r="R67" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 52)</t>
+          <t>spare (cop3 2)</t>
         </is>
       </c>
       <c r="S67" s="32" t="inlineStr"/>
@@ -8342,11 +8334,7 @@
       <c r="AB67" s="37" t="inlineStr"/>
       <c r="AC67" s="38" t="inlineStr"/>
       <c r="AD67" s="38" t="inlineStr"/>
-      <c r="AE67" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 52 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE67" s="38" t="inlineStr"/>
       <c r="AF67" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8370,20 +8358,20 @@
       </c>
       <c r="F68" s="41" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>cop4</t>
         </is>
       </c>
       <c r="G68" s="42" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+          <t>Ignition coil cyl 4</t>
         </is>
       </c>
       <c r="H68" s="41" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="I68" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J68" s="42" t="inlineStr"/>
@@ -8395,12 +8383,12 @@
       <c r="P68" s="45" t="inlineStr"/>
       <c r="Q68" s="46" t="inlineStr">
         <is>
-          <t>DRB102.53</t>
+          <t>cop4.2</t>
         </is>
       </c>
       <c r="R68" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 53)</t>
+          <t>spare (cop4 2)</t>
         </is>
       </c>
       <c r="S68" s="48" t="inlineStr"/>
@@ -8415,11 +8403,7 @@
       <c r="AB68" s="53" t="inlineStr"/>
       <c r="AC68" s="54" t="inlineStr"/>
       <c r="AD68" s="54" t="inlineStr"/>
-      <c r="AE68" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 53 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE68" s="54" t="inlineStr"/>
       <c r="AF68" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8443,16 +8427,16 @@
       </c>
       <c r="F69" s="25" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>ix_brail_s</t>
         </is>
       </c>
       <c r="G69" s="26" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+          <t>IX-B-RAIL inline plug, +5 V to B-engine</t>
         </is>
       </c>
       <c r="H69" s="25" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
@@ -8468,12 +8452,12 @@
       <c r="P69" s="29" t="inlineStr"/>
       <c r="Q69" s="30" t="inlineStr">
         <is>
-          <t>DRB102.57</t>
+          <t>ix_brail_p.4</t>
         </is>
       </c>
       <c r="R69" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 57)</t>
+          <t>spare (ix_brail_p 4)</t>
         </is>
       </c>
       <c r="S69" s="32" t="inlineStr"/>
@@ -8488,11 +8472,7 @@
       <c r="AB69" s="37" t="inlineStr"/>
       <c r="AC69" s="38" t="inlineStr"/>
       <c r="AD69" s="38" t="inlineStr"/>
-      <c r="AE69" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 57 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE69" s="38" t="inlineStr"/>
       <c r="AF69" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8516,16 +8496,16 @@
       </c>
       <c r="F70" s="41" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>ix_brail_s</t>
         </is>
       </c>
       <c r="G70" s="42" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+          <t>IX-B-RAIL inline plug, +5 V to B-engine</t>
         </is>
       </c>
       <c r="H70" s="41" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="I70" s="42" t="inlineStr">
         <is>
@@ -8541,12 +8521,12 @@
       <c r="P70" s="45" t="inlineStr"/>
       <c r="Q70" s="46" t="inlineStr">
         <is>
-          <t>DRB102.58</t>
+          <t>ix_brail_p.5</t>
         </is>
       </c>
       <c r="R70" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 58)</t>
+          <t>spare (ix_brail_p 5)</t>
         </is>
       </c>
       <c r="S70" s="48" t="inlineStr"/>
@@ -8561,11 +8541,7 @@
       <c r="AB70" s="53" t="inlineStr"/>
       <c r="AC70" s="54" t="inlineStr"/>
       <c r="AD70" s="54" t="inlineStr"/>
-      <c r="AE70" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 58 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE70" s="54" t="inlineStr"/>
       <c r="AF70" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8589,16 +8565,16 @@
       </c>
       <c r="F71" s="25" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>ix_brail_s</t>
         </is>
       </c>
       <c r="G71" s="26" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+          <t>IX-B-RAIL inline plug, +5 V to B-engine</t>
         </is>
       </c>
       <c r="H71" s="25" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
@@ -8614,12 +8590,12 @@
       <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>DRB102.59</t>
+          <t>ix_brail_p.6</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 59)</t>
+          <t>spare (ix_brail_p 6)</t>
         </is>
       </c>
       <c r="S71" s="32" t="inlineStr"/>
@@ -8634,11 +8610,7 @@
       <c r="AB71" s="37" t="inlineStr"/>
       <c r="AC71" s="38" t="inlineStr"/>
       <c r="AD71" s="38" t="inlineStr"/>
-      <c r="AE71" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 59 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE71" s="38" t="inlineStr"/>
       <c r="AF71" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8671,7 +8643,7 @@
         </is>
       </c>
       <c r="H72" s="41" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="I72" s="42" t="inlineStr">
         <is>
@@ -8687,12 +8659,12 @@
       <c r="P72" s="45" t="inlineStr"/>
       <c r="Q72" s="46" t="inlineStr">
         <is>
-          <t>DRB102.61</t>
+          <t>DRB102.3</t>
         </is>
       </c>
       <c r="R72" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 61)</t>
+          <t>spare (DRB102 3)</t>
         </is>
       </c>
       <c r="S72" s="48" t="inlineStr"/>
@@ -8709,7 +8681,7 @@
       <c r="AD72" s="54" t="inlineStr"/>
       <c r="AE72" s="54" t="inlineStr">
         <is>
-          <t>DRB102 61 = 'spare (size 16)'</t>
+          <t>DRB102 3 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF72" s="54" t="inlineStr">
@@ -8735,20 +8707,20 @@
       </c>
       <c r="F73" s="25" t="inlineStr">
         <is>
-          <t>cop1</t>
+          <t>bh_a_eng</t>
         </is>
       </c>
       <c r="G73" s="26" t="inlineStr">
         <is>
-          <t>Ignition coil cyl 1</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
         </is>
       </c>
       <c r="H73" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I73" s="26" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J73" s="26" t="inlineStr"/>
@@ -8760,12 +8732,12 @@
       <c r="P73" s="29" t="inlineStr"/>
       <c r="Q73" s="30" t="inlineStr">
         <is>
-          <t>cop1.2</t>
+          <t>DRB102.4</t>
         </is>
       </c>
       <c r="R73" s="31" t="inlineStr">
         <is>
-          <t>spare (cop1 2)</t>
+          <t>spare (DRB102 4)</t>
         </is>
       </c>
       <c r="S73" s="32" t="inlineStr"/>
@@ -8780,7 +8752,11 @@
       <c r="AB73" s="37" t="inlineStr"/>
       <c r="AC73" s="38" t="inlineStr"/>
       <c r="AD73" s="38" t="inlineStr"/>
-      <c r="AE73" s="38" t="inlineStr"/>
+      <c r="AE73" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 4 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF73" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8804,20 +8780,20 @@
       </c>
       <c r="F74" s="41" t="inlineStr">
         <is>
-          <t>cop2</t>
+          <t>bh_a_eng</t>
         </is>
       </c>
       <c r="G74" s="42" t="inlineStr">
         <is>
-          <t>Ignition coil cyl 2</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
         </is>
       </c>
       <c r="H74" s="41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I74" s="42" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J74" s="42" t="inlineStr"/>
@@ -8829,12 +8805,12 @@
       <c r="P74" s="45" t="inlineStr"/>
       <c r="Q74" s="46" t="inlineStr">
         <is>
-          <t>cop2.2</t>
+          <t>DRB102.5</t>
         </is>
       </c>
       <c r="R74" s="47" t="inlineStr">
         <is>
-          <t>spare (cop2 2)</t>
+          <t>spare (DRB102 5)</t>
         </is>
       </c>
       <c r="S74" s="48" t="inlineStr"/>
@@ -8849,7 +8825,11 @@
       <c r="AB74" s="53" t="inlineStr"/>
       <c r="AC74" s="54" t="inlineStr"/>
       <c r="AD74" s="54" t="inlineStr"/>
-      <c r="AE74" s="54" t="inlineStr"/>
+      <c r="AE74" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 5 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF74" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8873,20 +8853,20 @@
       </c>
       <c r="F75" s="25" t="inlineStr">
         <is>
-          <t>cop3</t>
+          <t>bh_a_eng</t>
         </is>
       </c>
       <c r="G75" s="26" t="inlineStr">
         <is>
-          <t>Ignition coil cyl 3</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
         </is>
       </c>
       <c r="H75" s="25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I75" s="26" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J75" s="26" t="inlineStr"/>
@@ -8898,12 +8878,12 @@
       <c r="P75" s="29" t="inlineStr"/>
       <c r="Q75" s="30" t="inlineStr">
         <is>
-          <t>cop3.2</t>
+          <t>DRB102.6</t>
         </is>
       </c>
       <c r="R75" s="31" t="inlineStr">
         <is>
-          <t>spare (cop3 2)</t>
+          <t>spare (DRB102 6)</t>
         </is>
       </c>
       <c r="S75" s="32" t="inlineStr"/>
@@ -8918,7 +8898,11 @@
       <c r="AB75" s="37" t="inlineStr"/>
       <c r="AC75" s="38" t="inlineStr"/>
       <c r="AD75" s="38" t="inlineStr"/>
-      <c r="AE75" s="38" t="inlineStr"/>
+      <c r="AE75" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 6 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF75" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8942,20 +8926,20 @@
       </c>
       <c r="F76" s="41" t="inlineStr">
         <is>
-          <t>cop4</t>
+          <t>bh_a_eng</t>
         </is>
       </c>
       <c r="G76" s="42" t="inlineStr">
         <is>
-          <t>Ignition coil cyl 4</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
         </is>
       </c>
       <c r="H76" s="41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I76" s="42" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J76" s="42" t="inlineStr"/>
@@ -8967,12 +8951,12 @@
       <c r="P76" s="45" t="inlineStr"/>
       <c r="Q76" s="46" t="inlineStr">
         <is>
-          <t>cop4.2</t>
+          <t>DRB102.7</t>
         </is>
       </c>
       <c r="R76" s="47" t="inlineStr">
         <is>
-          <t>spare (cop4 2)</t>
+          <t>spare (DRB102 7)</t>
         </is>
       </c>
       <c r="S76" s="48" t="inlineStr"/>
@@ -8987,7 +8971,11 @@
       <c r="AB76" s="53" t="inlineStr"/>
       <c r="AC76" s="54" t="inlineStr"/>
       <c r="AD76" s="54" t="inlineStr"/>
-      <c r="AE76" s="54" t="inlineStr"/>
+      <c r="AE76" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 7 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF76" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9011,16 +8999,16 @@
       </c>
       <c r="F77" s="25" t="inlineStr">
         <is>
-          <t>ix_brail_s</t>
+          <t>bh_a_eng</t>
         </is>
       </c>
       <c r="G77" s="26" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
         </is>
       </c>
       <c r="H77" s="25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I77" s="26" t="inlineStr">
         <is>
@@ -9036,12 +9024,12 @@
       <c r="P77" s="29" t="inlineStr"/>
       <c r="Q77" s="30" t="inlineStr">
         <is>
-          <t>ix_brail_p.4</t>
+          <t>DRB102.8</t>
         </is>
       </c>
       <c r="R77" s="31" t="inlineStr">
         <is>
-          <t>spare (ix_brail_p 4)</t>
+          <t>spare (DRB102 8)</t>
         </is>
       </c>
       <c r="S77" s="32" t="inlineStr"/>
@@ -9056,7 +9044,11 @@
       <c r="AB77" s="37" t="inlineStr"/>
       <c r="AC77" s="38" t="inlineStr"/>
       <c r="AD77" s="38" t="inlineStr"/>
-      <c r="AE77" s="38" t="inlineStr"/>
+      <c r="AE77" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 8 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF77" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9080,16 +9072,16 @@
       </c>
       <c r="F78" s="41" t="inlineStr">
         <is>
-          <t>ix_brail_s</t>
+          <t>bh_a_eng</t>
         </is>
       </c>
       <c r="G78" s="42" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
         </is>
       </c>
       <c r="H78" s="41" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I78" s="42" t="inlineStr">
         <is>
@@ -9105,12 +9097,12 @@
       <c r="P78" s="45" t="inlineStr"/>
       <c r="Q78" s="46" t="inlineStr">
         <is>
-          <t>ix_brail_p.5</t>
+          <t>DRB102.19</t>
         </is>
       </c>
       <c r="R78" s="47" t="inlineStr">
         <is>
-          <t>spare (ix_brail_p 5)</t>
+          <t>spare (DRB102 19)</t>
         </is>
       </c>
       <c r="S78" s="48" t="inlineStr"/>
@@ -9125,7 +9117,11 @@
       <c r="AB78" s="53" t="inlineStr"/>
       <c r="AC78" s="54" t="inlineStr"/>
       <c r="AD78" s="54" t="inlineStr"/>
-      <c r="AE78" s="54" t="inlineStr"/>
+      <c r="AE78" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 19 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF78" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9149,16 +9145,16 @@
       </c>
       <c r="F79" s="25" t="inlineStr">
         <is>
-          <t>ix_brail_s</t>
+          <t>bh_a_eng</t>
         </is>
       </c>
       <c r="G79" s="26" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
         </is>
       </c>
       <c r="H79" s="25" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I79" s="26" t="inlineStr">
         <is>
@@ -9174,12 +9170,12 @@
       <c r="P79" s="29" t="inlineStr"/>
       <c r="Q79" s="30" t="inlineStr">
         <is>
-          <t>ix_brail_p.6</t>
+          <t>DRB102.20</t>
         </is>
       </c>
       <c r="R79" s="31" t="inlineStr">
         <is>
-          <t>spare (ix_brail_p 6)</t>
+          <t>spare (DRB102 20)</t>
         </is>
       </c>
       <c r="S79" s="32" t="inlineStr"/>
@@ -9194,7 +9190,11 @@
       <c r="AB79" s="37" t="inlineStr"/>
       <c r="AC79" s="38" t="inlineStr"/>
       <c r="AD79" s="38" t="inlineStr"/>
-      <c r="AE79" s="38" t="inlineStr"/>
+      <c r="AE79" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 20 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF79" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9202,8 +9202,1468 @@
       </c>
       <c r="AG79" s="38" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" s="39" t="inlineStr"/>
+      <c r="B80" s="39" t="inlineStr"/>
+      <c r="C80" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D80" s="39" t="inlineStr"/>
+      <c r="E80" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F80" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G80" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H80" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="I80" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J80" s="42" t="inlineStr"/>
+      <c r="K80" s="43" t="inlineStr"/>
+      <c r="L80" s="44" t="inlineStr"/>
+      <c r="M80" s="45" t="inlineStr"/>
+      <c r="N80" s="44" t="inlineStr"/>
+      <c r="O80" s="45" t="inlineStr"/>
+      <c r="P80" s="45" t="inlineStr"/>
+      <c r="Q80" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.35</t>
+        </is>
+      </c>
+      <c r="R80" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 35)</t>
+        </is>
+      </c>
+      <c r="S80" s="48" t="inlineStr"/>
+      <c r="T80" s="48" t="inlineStr"/>
+      <c r="U80" s="49" t="inlineStr"/>
+      <c r="V80" s="50" t="inlineStr"/>
+      <c r="W80" s="50" t="inlineStr"/>
+      <c r="X80" s="50" t="inlineStr"/>
+      <c r="Y80" s="50" t="inlineStr"/>
+      <c r="Z80" s="51" t="inlineStr"/>
+      <c r="AA80" s="52" t="inlineStr"/>
+      <c r="AB80" s="53" t="inlineStr"/>
+      <c r="AC80" s="54" t="inlineStr"/>
+      <c r="AD80" s="54" t="inlineStr"/>
+      <c r="AE80" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 35 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF80" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG80" s="54" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr"/>
+      <c r="B81" s="23" t="inlineStr"/>
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="inlineStr"/>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F81" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G81" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H81" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="I81" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J81" s="26" t="inlineStr"/>
+      <c r="K81" s="27" t="inlineStr"/>
+      <c r="L81" s="28" t="inlineStr"/>
+      <c r="M81" s="29" t="inlineStr"/>
+      <c r="N81" s="28" t="inlineStr"/>
+      <c r="O81" s="29" t="inlineStr"/>
+      <c r="P81" s="29" t="inlineStr"/>
+      <c r="Q81" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.36</t>
+        </is>
+      </c>
+      <c r="R81" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 36)</t>
+        </is>
+      </c>
+      <c r="S81" s="32" t="inlineStr"/>
+      <c r="T81" s="32" t="inlineStr"/>
+      <c r="U81" s="33" t="inlineStr"/>
+      <c r="V81" s="34" t="inlineStr"/>
+      <c r="W81" s="34" t="inlineStr"/>
+      <c r="X81" s="34" t="inlineStr"/>
+      <c r="Y81" s="34" t="inlineStr"/>
+      <c r="Z81" s="35" t="inlineStr"/>
+      <c r="AA81" s="36" t="inlineStr"/>
+      <c r="AB81" s="37" t="inlineStr"/>
+      <c r="AC81" s="38" t="inlineStr"/>
+      <c r="AD81" s="38" t="inlineStr"/>
+      <c r="AE81" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 36 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF81" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG81" s="38" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="39" t="inlineStr"/>
+      <c r="B82" s="39" t="inlineStr"/>
+      <c r="C82" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D82" s="39" t="inlineStr"/>
+      <c r="E82" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F82" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G82" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H82" s="41" t="n">
+        <v>37</v>
+      </c>
+      <c r="I82" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J82" s="42" t="inlineStr"/>
+      <c r="K82" s="43" t="inlineStr"/>
+      <c r="L82" s="44" t="inlineStr"/>
+      <c r="M82" s="45" t="inlineStr"/>
+      <c r="N82" s="44" t="inlineStr"/>
+      <c r="O82" s="45" t="inlineStr"/>
+      <c r="P82" s="45" t="inlineStr"/>
+      <c r="Q82" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.37</t>
+        </is>
+      </c>
+      <c r="R82" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 37)</t>
+        </is>
+      </c>
+      <c r="S82" s="48" t="inlineStr"/>
+      <c r="T82" s="48" t="inlineStr"/>
+      <c r="U82" s="49" t="inlineStr"/>
+      <c r="V82" s="50" t="inlineStr"/>
+      <c r="W82" s="50" t="inlineStr"/>
+      <c r="X82" s="50" t="inlineStr"/>
+      <c r="Y82" s="50" t="inlineStr"/>
+      <c r="Z82" s="51" t="inlineStr"/>
+      <c r="AA82" s="52" t="inlineStr"/>
+      <c r="AB82" s="53" t="inlineStr"/>
+      <c r="AC82" s="54" t="inlineStr"/>
+      <c r="AD82" s="54" t="inlineStr"/>
+      <c r="AE82" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 37 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF82" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG82" s="54" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="inlineStr"/>
+      <c r="B83" s="23" t="inlineStr"/>
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D83" s="23" t="inlineStr"/>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F83" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G83" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H83" s="25" t="n">
+        <v>38</v>
+      </c>
+      <c r="I83" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J83" s="26" t="inlineStr"/>
+      <c r="K83" s="27" t="inlineStr"/>
+      <c r="L83" s="28" t="inlineStr"/>
+      <c r="M83" s="29" t="inlineStr"/>
+      <c r="N83" s="28" t="inlineStr"/>
+      <c r="O83" s="29" t="inlineStr"/>
+      <c r="P83" s="29" t="inlineStr"/>
+      <c r="Q83" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.38</t>
+        </is>
+      </c>
+      <c r="R83" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 38)</t>
+        </is>
+      </c>
+      <c r="S83" s="32" t="inlineStr"/>
+      <c r="T83" s="32" t="inlineStr"/>
+      <c r="U83" s="33" t="inlineStr"/>
+      <c r="V83" s="34" t="inlineStr"/>
+      <c r="W83" s="34" t="inlineStr"/>
+      <c r="X83" s="34" t="inlineStr"/>
+      <c r="Y83" s="34" t="inlineStr"/>
+      <c r="Z83" s="35" t="inlineStr"/>
+      <c r="AA83" s="36" t="inlineStr"/>
+      <c r="AB83" s="37" t="inlineStr"/>
+      <c r="AC83" s="38" t="inlineStr"/>
+      <c r="AD83" s="38" t="inlineStr"/>
+      <c r="AE83" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 38 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF83" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG83" s="38" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="39" t="inlineStr"/>
+      <c r="B84" s="39" t="inlineStr"/>
+      <c r="C84" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D84" s="39" t="inlineStr"/>
+      <c r="E84" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F84" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G84" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H84" s="41" t="n">
+        <v>39</v>
+      </c>
+      <c r="I84" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J84" s="42" t="inlineStr"/>
+      <c r="K84" s="43" t="inlineStr"/>
+      <c r="L84" s="44" t="inlineStr"/>
+      <c r="M84" s="45" t="inlineStr"/>
+      <c r="N84" s="44" t="inlineStr"/>
+      <c r="O84" s="45" t="inlineStr"/>
+      <c r="P84" s="45" t="inlineStr"/>
+      <c r="Q84" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.39</t>
+        </is>
+      </c>
+      <c r="R84" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 39)</t>
+        </is>
+      </c>
+      <c r="S84" s="48" t="inlineStr"/>
+      <c r="T84" s="48" t="inlineStr"/>
+      <c r="U84" s="49" t="inlineStr"/>
+      <c r="V84" s="50" t="inlineStr"/>
+      <c r="W84" s="50" t="inlineStr"/>
+      <c r="X84" s="50" t="inlineStr"/>
+      <c r="Y84" s="50" t="inlineStr"/>
+      <c r="Z84" s="51" t="inlineStr"/>
+      <c r="AA84" s="52" t="inlineStr"/>
+      <c r="AB84" s="53" t="inlineStr"/>
+      <c r="AC84" s="54" t="inlineStr"/>
+      <c r="AD84" s="54" t="inlineStr"/>
+      <c r="AE84" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 39 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF84" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG84" s="54" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="inlineStr"/>
+      <c r="B85" s="23" t="inlineStr"/>
+      <c r="C85" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D85" s="23" t="inlineStr"/>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F85" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G85" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H85" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="I85" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J85" s="26" t="inlineStr"/>
+      <c r="K85" s="27" t="inlineStr"/>
+      <c r="L85" s="28" t="inlineStr"/>
+      <c r="M85" s="29" t="inlineStr"/>
+      <c r="N85" s="28" t="inlineStr"/>
+      <c r="O85" s="29" t="inlineStr"/>
+      <c r="P85" s="29" t="inlineStr"/>
+      <c r="Q85" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.40</t>
+        </is>
+      </c>
+      <c r="R85" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 40)</t>
+        </is>
+      </c>
+      <c r="S85" s="32" t="inlineStr"/>
+      <c r="T85" s="32" t="inlineStr"/>
+      <c r="U85" s="33" t="inlineStr"/>
+      <c r="V85" s="34" t="inlineStr"/>
+      <c r="W85" s="34" t="inlineStr"/>
+      <c r="X85" s="34" t="inlineStr"/>
+      <c r="Y85" s="34" t="inlineStr"/>
+      <c r="Z85" s="35" t="inlineStr"/>
+      <c r="AA85" s="36" t="inlineStr"/>
+      <c r="AB85" s="37" t="inlineStr"/>
+      <c r="AC85" s="38" t="inlineStr"/>
+      <c r="AD85" s="38" t="inlineStr"/>
+      <c r="AE85" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 40 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF85" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG85" s="38" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="39" t="inlineStr"/>
+      <c r="B86" s="39" t="inlineStr"/>
+      <c r="C86" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D86" s="39" t="inlineStr"/>
+      <c r="E86" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F86" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G86" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H86" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="I86" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J86" s="42" t="inlineStr"/>
+      <c r="K86" s="43" t="inlineStr"/>
+      <c r="L86" s="44" t="inlineStr"/>
+      <c r="M86" s="45" t="inlineStr"/>
+      <c r="N86" s="44" t="inlineStr"/>
+      <c r="O86" s="45" t="inlineStr"/>
+      <c r="P86" s="45" t="inlineStr"/>
+      <c r="Q86" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.43</t>
+        </is>
+      </c>
+      <c r="R86" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 43)</t>
+        </is>
+      </c>
+      <c r="S86" s="48" t="inlineStr"/>
+      <c r="T86" s="48" t="inlineStr"/>
+      <c r="U86" s="49" t="inlineStr"/>
+      <c r="V86" s="50" t="inlineStr"/>
+      <c r="W86" s="50" t="inlineStr"/>
+      <c r="X86" s="50" t="inlineStr"/>
+      <c r="Y86" s="50" t="inlineStr"/>
+      <c r="Z86" s="51" t="inlineStr"/>
+      <c r="AA86" s="52" t="inlineStr"/>
+      <c r="AB86" s="53" t="inlineStr"/>
+      <c r="AC86" s="54" t="inlineStr"/>
+      <c r="AD86" s="54" t="inlineStr"/>
+      <c r="AE86" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 43 = 'spare (size 4)'</t>
+        </is>
+      </c>
+      <c r="AF86" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG86" s="54" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr"/>
+      <c r="B87" s="23" t="inlineStr"/>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="inlineStr"/>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F87" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G87" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H87" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="I87" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J87" s="26" t="inlineStr"/>
+      <c r="K87" s="27" t="inlineStr"/>
+      <c r="L87" s="28" t="inlineStr"/>
+      <c r="M87" s="29" t="inlineStr"/>
+      <c r="N87" s="28" t="inlineStr"/>
+      <c r="O87" s="29" t="inlineStr"/>
+      <c r="P87" s="29" t="inlineStr"/>
+      <c r="Q87" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.48</t>
+        </is>
+      </c>
+      <c r="R87" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 48)</t>
+        </is>
+      </c>
+      <c r="S87" s="32" t="inlineStr"/>
+      <c r="T87" s="32" t="inlineStr"/>
+      <c r="U87" s="33" t="inlineStr"/>
+      <c r="V87" s="34" t="inlineStr"/>
+      <c r="W87" s="34" t="inlineStr"/>
+      <c r="X87" s="34" t="inlineStr"/>
+      <c r="Y87" s="34" t="inlineStr"/>
+      <c r="Z87" s="35" t="inlineStr"/>
+      <c r="AA87" s="36" t="inlineStr"/>
+      <c r="AB87" s="37" t="inlineStr"/>
+      <c r="AC87" s="38" t="inlineStr"/>
+      <c r="AD87" s="38" t="inlineStr"/>
+      <c r="AE87" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 48 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF87" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG87" s="38" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="39" t="inlineStr"/>
+      <c r="B88" s="39" t="inlineStr"/>
+      <c r="C88" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D88" s="39" t="inlineStr"/>
+      <c r="E88" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F88" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G88" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H88" s="41" t="n">
+        <v>49</v>
+      </c>
+      <c r="I88" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J88" s="42" t="inlineStr"/>
+      <c r="K88" s="43" t="inlineStr"/>
+      <c r="L88" s="44" t="inlineStr"/>
+      <c r="M88" s="45" t="inlineStr"/>
+      <c r="N88" s="44" t="inlineStr"/>
+      <c r="O88" s="45" t="inlineStr"/>
+      <c r="P88" s="45" t="inlineStr"/>
+      <c r="Q88" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.49</t>
+        </is>
+      </c>
+      <c r="R88" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 49)</t>
+        </is>
+      </c>
+      <c r="S88" s="48" t="inlineStr"/>
+      <c r="T88" s="48" t="inlineStr"/>
+      <c r="U88" s="49" t="inlineStr"/>
+      <c r="V88" s="50" t="inlineStr"/>
+      <c r="W88" s="50" t="inlineStr"/>
+      <c r="X88" s="50" t="inlineStr"/>
+      <c r="Y88" s="50" t="inlineStr"/>
+      <c r="Z88" s="51" t="inlineStr"/>
+      <c r="AA88" s="52" t="inlineStr"/>
+      <c r="AB88" s="53" t="inlineStr"/>
+      <c r="AC88" s="54" t="inlineStr"/>
+      <c r="AD88" s="54" t="inlineStr"/>
+      <c r="AE88" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 49 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF88" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG88" s="54" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="inlineStr"/>
+      <c r="B89" s="23" t="inlineStr"/>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D89" s="23" t="inlineStr"/>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F89" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G89" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H89" s="25" t="n">
+        <v>54</v>
+      </c>
+      <c r="I89" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J89" s="26" t="inlineStr"/>
+      <c r="K89" s="27" t="inlineStr"/>
+      <c r="L89" s="28" t="inlineStr"/>
+      <c r="M89" s="29" t="inlineStr"/>
+      <c r="N89" s="28" t="inlineStr"/>
+      <c r="O89" s="29" t="inlineStr"/>
+      <c r="P89" s="29" t="inlineStr"/>
+      <c r="Q89" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.54</t>
+        </is>
+      </c>
+      <c r="R89" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 54)</t>
+        </is>
+      </c>
+      <c r="S89" s="32" t="inlineStr"/>
+      <c r="T89" s="32" t="inlineStr"/>
+      <c r="U89" s="33" t="inlineStr"/>
+      <c r="V89" s="34" t="inlineStr"/>
+      <c r="W89" s="34" t="inlineStr"/>
+      <c r="X89" s="34" t="inlineStr"/>
+      <c r="Y89" s="34" t="inlineStr"/>
+      <c r="Z89" s="35" t="inlineStr"/>
+      <c r="AA89" s="36" t="inlineStr"/>
+      <c r="AB89" s="37" t="inlineStr"/>
+      <c r="AC89" s="38" t="inlineStr"/>
+      <c r="AD89" s="38" t="inlineStr"/>
+      <c r="AE89" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 54 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF89" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG89" s="38" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="39" t="inlineStr"/>
+      <c r="B90" s="39" t="inlineStr"/>
+      <c r="C90" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D90" s="39" t="inlineStr"/>
+      <c r="E90" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F90" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G90" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H90" s="41" t="n">
+        <v>55</v>
+      </c>
+      <c r="I90" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J90" s="42" t="inlineStr"/>
+      <c r="K90" s="43" t="inlineStr"/>
+      <c r="L90" s="44" t="inlineStr"/>
+      <c r="M90" s="45" t="inlineStr"/>
+      <c r="N90" s="44" t="inlineStr"/>
+      <c r="O90" s="45" t="inlineStr"/>
+      <c r="P90" s="45" t="inlineStr"/>
+      <c r="Q90" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.55</t>
+        </is>
+      </c>
+      <c r="R90" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 55)</t>
+        </is>
+      </c>
+      <c r="S90" s="48" t="inlineStr"/>
+      <c r="T90" s="48" t="inlineStr"/>
+      <c r="U90" s="49" t="inlineStr"/>
+      <c r="V90" s="50" t="inlineStr"/>
+      <c r="W90" s="50" t="inlineStr"/>
+      <c r="X90" s="50" t="inlineStr"/>
+      <c r="Y90" s="50" t="inlineStr"/>
+      <c r="Z90" s="51" t="inlineStr"/>
+      <c r="AA90" s="52" t="inlineStr"/>
+      <c r="AB90" s="53" t="inlineStr"/>
+      <c r="AC90" s="54" t="inlineStr"/>
+      <c r="AD90" s="54" t="inlineStr"/>
+      <c r="AE90" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 55 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF90" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG90" s="54" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="inlineStr"/>
+      <c r="B91" s="23" t="inlineStr"/>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="inlineStr"/>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F91" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G91" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H91" s="25" t="n">
+        <v>86</v>
+      </c>
+      <c r="I91" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J91" s="26" t="inlineStr"/>
+      <c r="K91" s="27" t="inlineStr"/>
+      <c r="L91" s="28" t="inlineStr"/>
+      <c r="M91" s="29" t="inlineStr"/>
+      <c r="N91" s="28" t="inlineStr"/>
+      <c r="O91" s="29" t="inlineStr"/>
+      <c r="P91" s="29" t="inlineStr"/>
+      <c r="Q91" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.86</t>
+        </is>
+      </c>
+      <c r="R91" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 86)</t>
+        </is>
+      </c>
+      <c r="S91" s="32" t="inlineStr"/>
+      <c r="T91" s="32" t="inlineStr"/>
+      <c r="U91" s="33" t="inlineStr"/>
+      <c r="V91" s="34" t="inlineStr"/>
+      <c r="W91" s="34" t="inlineStr"/>
+      <c r="X91" s="34" t="inlineStr"/>
+      <c r="Y91" s="34" t="inlineStr"/>
+      <c r="Z91" s="35" t="inlineStr"/>
+      <c r="AA91" s="36" t="inlineStr"/>
+      <c r="AB91" s="37" t="inlineStr"/>
+      <c r="AC91" s="38" t="inlineStr"/>
+      <c r="AD91" s="38" t="inlineStr"/>
+      <c r="AE91" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 86 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF91" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG91" s="38" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="39" t="inlineStr"/>
+      <c r="B92" s="39" t="inlineStr"/>
+      <c r="C92" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D92" s="39" t="inlineStr"/>
+      <c r="E92" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F92" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G92" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H92" s="41" t="n">
+        <v>87</v>
+      </c>
+      <c r="I92" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J92" s="42" t="inlineStr"/>
+      <c r="K92" s="43" t="inlineStr"/>
+      <c r="L92" s="44" t="inlineStr"/>
+      <c r="M92" s="45" t="inlineStr"/>
+      <c r="N92" s="44" t="inlineStr"/>
+      <c r="O92" s="45" t="inlineStr"/>
+      <c r="P92" s="45" t="inlineStr"/>
+      <c r="Q92" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.87</t>
+        </is>
+      </c>
+      <c r="R92" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 87)</t>
+        </is>
+      </c>
+      <c r="S92" s="48" t="inlineStr"/>
+      <c r="T92" s="48" t="inlineStr"/>
+      <c r="U92" s="49" t="inlineStr"/>
+      <c r="V92" s="50" t="inlineStr"/>
+      <c r="W92" s="50" t="inlineStr"/>
+      <c r="X92" s="50" t="inlineStr"/>
+      <c r="Y92" s="50" t="inlineStr"/>
+      <c r="Z92" s="51" t="inlineStr"/>
+      <c r="AA92" s="52" t="inlineStr"/>
+      <c r="AB92" s="53" t="inlineStr"/>
+      <c r="AC92" s="54" t="inlineStr"/>
+      <c r="AD92" s="54" t="inlineStr"/>
+      <c r="AE92" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 87 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF92" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG92" s="54" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="inlineStr"/>
+      <c r="B93" s="23" t="inlineStr"/>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D93" s="23" t="inlineStr"/>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F93" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G93" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H93" s="25" t="n">
+        <v>88</v>
+      </c>
+      <c r="I93" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J93" s="26" t="inlineStr"/>
+      <c r="K93" s="27" t="inlineStr"/>
+      <c r="L93" s="28" t="inlineStr"/>
+      <c r="M93" s="29" t="inlineStr"/>
+      <c r="N93" s="28" t="inlineStr"/>
+      <c r="O93" s="29" t="inlineStr"/>
+      <c r="P93" s="29" t="inlineStr"/>
+      <c r="Q93" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.88</t>
+        </is>
+      </c>
+      <c r="R93" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 88)</t>
+        </is>
+      </c>
+      <c r="S93" s="32" t="inlineStr"/>
+      <c r="T93" s="32" t="inlineStr"/>
+      <c r="U93" s="33" t="inlineStr"/>
+      <c r="V93" s="34" t="inlineStr"/>
+      <c r="W93" s="34" t="inlineStr"/>
+      <c r="X93" s="34" t="inlineStr"/>
+      <c r="Y93" s="34" t="inlineStr"/>
+      <c r="Z93" s="35" t="inlineStr"/>
+      <c r="AA93" s="36" t="inlineStr"/>
+      <c r="AB93" s="37" t="inlineStr"/>
+      <c r="AC93" s="38" t="inlineStr"/>
+      <c r="AD93" s="38" t="inlineStr"/>
+      <c r="AE93" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 88 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF93" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG93" s="38" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="39" t="inlineStr"/>
+      <c r="B94" s="39" t="inlineStr"/>
+      <c r="C94" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D94" s="39" t="inlineStr"/>
+      <c r="E94" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F94" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G94" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H94" s="41" t="n">
+        <v>89</v>
+      </c>
+      <c r="I94" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J94" s="42" t="inlineStr"/>
+      <c r="K94" s="43" t="inlineStr"/>
+      <c r="L94" s="44" t="inlineStr"/>
+      <c r="M94" s="45" t="inlineStr"/>
+      <c r="N94" s="44" t="inlineStr"/>
+      <c r="O94" s="45" t="inlineStr"/>
+      <c r="P94" s="45" t="inlineStr"/>
+      <c r="Q94" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.89</t>
+        </is>
+      </c>
+      <c r="R94" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 89)</t>
+        </is>
+      </c>
+      <c r="S94" s="48" t="inlineStr"/>
+      <c r="T94" s="48" t="inlineStr"/>
+      <c r="U94" s="49" t="inlineStr"/>
+      <c r="V94" s="50" t="inlineStr"/>
+      <c r="W94" s="50" t="inlineStr"/>
+      <c r="X94" s="50" t="inlineStr"/>
+      <c r="Y94" s="50" t="inlineStr"/>
+      <c r="Z94" s="51" t="inlineStr"/>
+      <c r="AA94" s="52" t="inlineStr"/>
+      <c r="AB94" s="53" t="inlineStr"/>
+      <c r="AC94" s="54" t="inlineStr"/>
+      <c r="AD94" s="54" t="inlineStr"/>
+      <c r="AE94" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 89 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF94" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG94" s="54" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="inlineStr"/>
+      <c r="B95" s="23" t="inlineStr"/>
+      <c r="C95" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D95" s="23" t="inlineStr"/>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F95" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G95" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H95" s="25" t="n">
+        <v>90</v>
+      </c>
+      <c r="I95" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J95" s="26" t="inlineStr"/>
+      <c r="K95" s="27" t="inlineStr"/>
+      <c r="L95" s="28" t="inlineStr"/>
+      <c r="M95" s="29" t="inlineStr"/>
+      <c r="N95" s="28" t="inlineStr"/>
+      <c r="O95" s="29" t="inlineStr"/>
+      <c r="P95" s="29" t="inlineStr"/>
+      <c r="Q95" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.90</t>
+        </is>
+      </c>
+      <c r="R95" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 90)</t>
+        </is>
+      </c>
+      <c r="S95" s="32" t="inlineStr"/>
+      <c r="T95" s="32" t="inlineStr"/>
+      <c r="U95" s="33" t="inlineStr"/>
+      <c r="V95" s="34" t="inlineStr"/>
+      <c r="W95" s="34" t="inlineStr"/>
+      <c r="X95" s="34" t="inlineStr"/>
+      <c r="Y95" s="34" t="inlineStr"/>
+      <c r="Z95" s="35" t="inlineStr"/>
+      <c r="AA95" s="36" t="inlineStr"/>
+      <c r="AB95" s="37" t="inlineStr"/>
+      <c r="AC95" s="38" t="inlineStr"/>
+      <c r="AD95" s="38" t="inlineStr"/>
+      <c r="AE95" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 90 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF95" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG95" s="38" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="39" t="inlineStr"/>
+      <c r="B96" s="39" t="inlineStr"/>
+      <c r="C96" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D96" s="39" t="inlineStr"/>
+      <c r="E96" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F96" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G96" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H96" s="41" t="n">
+        <v>91</v>
+      </c>
+      <c r="I96" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J96" s="42" t="inlineStr"/>
+      <c r="K96" s="43" t="inlineStr"/>
+      <c r="L96" s="44" t="inlineStr"/>
+      <c r="M96" s="45" t="inlineStr"/>
+      <c r="N96" s="44" t="inlineStr"/>
+      <c r="O96" s="45" t="inlineStr"/>
+      <c r="P96" s="45" t="inlineStr"/>
+      <c r="Q96" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.91</t>
+        </is>
+      </c>
+      <c r="R96" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 91)</t>
+        </is>
+      </c>
+      <c r="S96" s="48" t="inlineStr"/>
+      <c r="T96" s="48" t="inlineStr"/>
+      <c r="U96" s="49" t="inlineStr"/>
+      <c r="V96" s="50" t="inlineStr"/>
+      <c r="W96" s="50" t="inlineStr"/>
+      <c r="X96" s="50" t="inlineStr"/>
+      <c r="Y96" s="50" t="inlineStr"/>
+      <c r="Z96" s="51" t="inlineStr"/>
+      <c r="AA96" s="52" t="inlineStr"/>
+      <c r="AB96" s="53" t="inlineStr"/>
+      <c r="AC96" s="54" t="inlineStr"/>
+      <c r="AD96" s="54" t="inlineStr"/>
+      <c r="AE96" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 91 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF96" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG96" s="54" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="23" t="inlineStr"/>
+      <c r="B97" s="23" t="inlineStr"/>
+      <c r="C97" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D97" s="23" t="inlineStr"/>
+      <c r="E97" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F97" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G97" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H97" s="25" t="n">
+        <v>92</v>
+      </c>
+      <c r="I97" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J97" s="26" t="inlineStr"/>
+      <c r="K97" s="27" t="inlineStr"/>
+      <c r="L97" s="28" t="inlineStr"/>
+      <c r="M97" s="29" t="inlineStr"/>
+      <c r="N97" s="28" t="inlineStr"/>
+      <c r="O97" s="29" t="inlineStr"/>
+      <c r="P97" s="29" t="inlineStr"/>
+      <c r="Q97" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.92</t>
+        </is>
+      </c>
+      <c r="R97" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 92)</t>
+        </is>
+      </c>
+      <c r="S97" s="32" t="inlineStr"/>
+      <c r="T97" s="32" t="inlineStr"/>
+      <c r="U97" s="33" t="inlineStr"/>
+      <c r="V97" s="34" t="inlineStr"/>
+      <c r="W97" s="34" t="inlineStr"/>
+      <c r="X97" s="34" t="inlineStr"/>
+      <c r="Y97" s="34" t="inlineStr"/>
+      <c r="Z97" s="35" t="inlineStr"/>
+      <c r="AA97" s="36" t="inlineStr"/>
+      <c r="AB97" s="37" t="inlineStr"/>
+      <c r="AC97" s="38" t="inlineStr"/>
+      <c r="AD97" s="38" t="inlineStr"/>
+      <c r="AE97" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 92 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF97" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG97" s="38" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="39" t="inlineStr"/>
+      <c r="B98" s="39" t="inlineStr"/>
+      <c r="C98" s="39" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D98" s="39" t="inlineStr"/>
+      <c r="E98" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F98" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G98" s="42" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H98" s="41" t="n">
+        <v>93</v>
+      </c>
+      <c r="I98" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J98" s="42" t="inlineStr"/>
+      <c r="K98" s="43" t="inlineStr"/>
+      <c r="L98" s="44" t="inlineStr"/>
+      <c r="M98" s="45" t="inlineStr"/>
+      <c r="N98" s="44" t="inlineStr"/>
+      <c r="O98" s="45" t="inlineStr"/>
+      <c r="P98" s="45" t="inlineStr"/>
+      <c r="Q98" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.93</t>
+        </is>
+      </c>
+      <c r="R98" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 93)</t>
+        </is>
+      </c>
+      <c r="S98" s="48" t="inlineStr"/>
+      <c r="T98" s="48" t="inlineStr"/>
+      <c r="U98" s="49" t="inlineStr"/>
+      <c r="V98" s="50" t="inlineStr"/>
+      <c r="W98" s="50" t="inlineStr"/>
+      <c r="X98" s="50" t="inlineStr"/>
+      <c r="Y98" s="50" t="inlineStr"/>
+      <c r="Z98" s="51" t="inlineStr"/>
+      <c r="AA98" s="52" t="inlineStr"/>
+      <c r="AB98" s="53" t="inlineStr"/>
+      <c r="AC98" s="54" t="inlineStr"/>
+      <c r="AD98" s="54" t="inlineStr"/>
+      <c r="AE98" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 93 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF98" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG98" s="54" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="23" t="inlineStr"/>
+      <c r="B99" s="23" t="inlineStr"/>
+      <c r="C99" s="23" t="inlineStr">
+        <is>
+          <t>A-engine</t>
+        </is>
+      </c>
+      <c r="D99" s="23" t="inlineStr"/>
+      <c r="E99" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F99" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_eng</t>
+        </is>
+      </c>
+      <c r="G99" s="26" t="inlineStr">
+        <is>
+          <t>Bulkhead BH-A (DRB102, RH firewall)</t>
+        </is>
+      </c>
+      <c r="H99" s="25" t="n">
+        <v>94</v>
+      </c>
+      <c r="I99" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J99" s="26" t="inlineStr"/>
+      <c r="K99" s="27" t="inlineStr"/>
+      <c r="L99" s="28" t="inlineStr"/>
+      <c r="M99" s="29" t="inlineStr"/>
+      <c r="N99" s="28" t="inlineStr"/>
+      <c r="O99" s="29" t="inlineStr"/>
+      <c r="P99" s="29" t="inlineStr"/>
+      <c r="Q99" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.94</t>
+        </is>
+      </c>
+      <c r="R99" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 94)</t>
+        </is>
+      </c>
+      <c r="S99" s="32" t="inlineStr"/>
+      <c r="T99" s="32" t="inlineStr"/>
+      <c r="U99" s="33" t="inlineStr"/>
+      <c r="V99" s="34" t="inlineStr"/>
+      <c r="W99" s="34" t="inlineStr"/>
+      <c r="X99" s="34" t="inlineStr"/>
+      <c r="Y99" s="34" t="inlineStr"/>
+      <c r="Z99" s="35" t="inlineStr"/>
+      <c r="AA99" s="36" t="inlineStr"/>
+      <c r="AB99" s="37" t="inlineStr"/>
+      <c r="AC99" s="38" t="inlineStr"/>
+      <c r="AD99" s="38" t="inlineStr"/>
+      <c r="AE99" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 94 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF99" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG99" s="38" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AG79"/>
+  <autoFilter ref="A2:AG99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -9364,7 +10824,7 @@
       </c>
       <c r="B3" s="55" t="inlineStr">
         <is>
-          <t>Switched +12 V splice - BH-A pin 20 to boost solenoid and flex sensor</t>
+          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
@@ -9420,7 +10880,7 @@
       </c>
       <c r="B4" s="57" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 26 (ECU A24) to coolant temp, intake temp, throttle</t>
+          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
         </is>
       </c>
       <c r="C4" s="39" t="inlineStr">
@@ -9532,7 +10992,7 @@
       </c>
       <c r="B6" s="57" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 1 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
@@ -9588,7 +11048,7 @@
       </c>
       <c r="B7" s="55" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 2 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -9644,7 +11104,7 @@
       </c>
       <c r="B8" s="57" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 29 (ECU A24) to MAP and flex sensor</t>
+          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
         </is>
       </c>
       <c r="C8" s="39" t="inlineStr">
@@ -9822,7 +11282,7 @@
       </c>
       <c r="G3" s="36" t="inlineStr">
         <is>
-          <t>shared DRB102 (section A here, section B on B-engine)</t>
+          <t>shared DRB102 (loom A wires here, loom B wires on B-engine)</t>
         </is>
       </c>
     </row>
@@ -10450,7 +11910,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="26" t="inlineStr">
         <is>
@@ -10468,7 +11928,7 @@
         </is>
       </c>
       <c r="G3" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="29" t="inlineStr">
         <is>
@@ -10498,7 +11958,7 @@
         </is>
       </c>
       <c r="C4" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
@@ -10516,7 +11976,7 @@
         </is>
       </c>
       <c r="G4" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="45" t="inlineStr">
         <is>
@@ -10546,7 +12006,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
@@ -10564,7 +12024,7 @@
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
@@ -10594,7 +12054,7 @@
         </is>
       </c>
       <c r="C6" s="41" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
@@ -10612,7 +12072,7 @@
         </is>
       </c>
       <c r="G6" s="44" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="H6" s="45" t="inlineStr">
         <is>
@@ -10642,7 +12102,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
@@ -10660,7 +12120,7 @@
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
@@ -10690,7 +12150,7 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
@@ -10708,7 +12168,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="H8" s="45" t="inlineStr">
         <is>
@@ -10738,7 +12198,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
@@ -10756,7 +12216,7 @@
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
@@ -10786,7 +12246,7 @@
         </is>
       </c>
       <c r="C10" s="41" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
@@ -10804,7 +12264,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H10" s="45" t="inlineStr">
         <is>
@@ -10834,7 +12294,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
@@ -10852,7 +12312,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
@@ -10882,7 +12342,7 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
@@ -10900,7 +12360,7 @@
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H12" s="45" t="inlineStr">
         <is>
@@ -10930,7 +12390,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
@@ -10948,7 +12408,7 @@
         </is>
       </c>
       <c r="G13" s="28" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
@@ -10978,7 +12438,7 @@
         </is>
       </c>
       <c r="C14" s="41" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D14" s="42" t="inlineStr">
         <is>
@@ -10996,7 +12456,7 @@
         </is>
       </c>
       <c r="G14" s="44" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
@@ -11026,7 +12486,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
@@ -11044,7 +12504,7 @@
         </is>
       </c>
       <c r="G15" s="28" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
@@ -11074,7 +12534,7 @@
         </is>
       </c>
       <c r="C16" s="41" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
@@ -11092,7 +12552,7 @@
         </is>
       </c>
       <c r="G16" s="44" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" s="45" t="inlineStr">
         <is>
@@ -11122,7 +12582,7 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
@@ -11140,7 +12600,7 @@
         </is>
       </c>
       <c r="G17" s="28" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
@@ -11170,7 +12630,7 @@
         </is>
       </c>
       <c r="C18" s="41" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D18" s="42" t="inlineStr">
         <is>
@@ -11188,7 +12648,7 @@
         </is>
       </c>
       <c r="G18" s="44" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H18" s="45" t="inlineStr">
         <is>
@@ -11218,7 +12678,7 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
@@ -11236,7 +12696,7 @@
         </is>
       </c>
       <c r="G19" s="28" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
@@ -11266,7 +12726,7 @@
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D20" s="42" t="inlineStr">
         <is>
@@ -11284,7 +12744,7 @@
         </is>
       </c>
       <c r="G20" s="44" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H20" s="45" t="inlineStr">
         <is>
@@ -11314,7 +12774,7 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
@@ -11332,7 +12792,7 @@
         </is>
       </c>
       <c r="G21" s="28" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
@@ -11362,7 +12822,7 @@
         </is>
       </c>
       <c r="C22" s="41" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D22" s="42" t="inlineStr">
         <is>
@@ -11380,7 +12840,7 @@
         </is>
       </c>
       <c r="G22" s="44" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H22" s="45" t="inlineStr">
         <is>
@@ -11410,7 +12870,7 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
@@ -11428,7 +12888,7 @@
         </is>
       </c>
       <c r="G23" s="28" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H23" s="29" t="inlineStr">
         <is>
@@ -11458,7 +12918,7 @@
         </is>
       </c>
       <c r="C24" s="41" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D24" s="42" t="inlineStr">
         <is>
@@ -11476,7 +12936,7 @@
         </is>
       </c>
       <c r="G24" s="44" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H24" s="45" t="inlineStr">
         <is>
@@ -11506,7 +12966,7 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
@@ -11524,7 +12984,7 @@
         </is>
       </c>
       <c r="G25" s="28" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H25" s="29" t="inlineStr">
         <is>
@@ -11554,7 +13014,7 @@
         </is>
       </c>
       <c r="C26" s="41" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D26" s="42" t="inlineStr">
         <is>
@@ -11572,7 +13032,7 @@
         </is>
       </c>
       <c r="G26" s="44" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H26" s="45" t="inlineStr">
         <is>
@@ -11602,7 +13062,7 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
@@ -11620,7 +13080,7 @@
         </is>
       </c>
       <c r="G27" s="28" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H27" s="29" t="inlineStr">
         <is>
@@ -11650,7 +13110,7 @@
         </is>
       </c>
       <c r="C28" s="41" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D28" s="42" t="inlineStr">
         <is>
@@ -11668,7 +13128,7 @@
         </is>
       </c>
       <c r="G28" s="44" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H28" s="45" t="inlineStr">
         <is>
@@ -11698,7 +13158,7 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
@@ -11716,7 +13176,7 @@
         </is>
       </c>
       <c r="G29" s="28" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
@@ -11746,7 +13206,7 @@
         </is>
       </c>
       <c r="C30" s="41" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D30" s="42" t="inlineStr">
         <is>
@@ -11764,7 +13224,7 @@
         </is>
       </c>
       <c r="G30" s="44" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H30" s="45" t="inlineStr">
         <is>
@@ -11794,7 +13254,7 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
@@ -11812,7 +13272,7 @@
         </is>
       </c>
       <c r="G31" s="28" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
@@ -11842,7 +13302,7 @@
         </is>
       </c>
       <c r="C32" s="41" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D32" s="42" t="inlineStr">
         <is>
@@ -11860,7 +13320,7 @@
         </is>
       </c>
       <c r="G32" s="44" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H32" s="45" t="inlineStr">
         <is>
@@ -11890,7 +13350,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
@@ -11908,7 +13368,7 @@
         </is>
       </c>
       <c r="G33" s="28" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
@@ -11938,7 +13398,7 @@
         </is>
       </c>
       <c r="C34" s="41" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D34" s="42" t="inlineStr">
         <is>
@@ -11956,7 +13416,7 @@
         </is>
       </c>
       <c r="G34" s="44" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H34" s="45" t="inlineStr">
         <is>
@@ -11986,7 +13446,7 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
@@ -12004,7 +13464,7 @@
         </is>
       </c>
       <c r="G35" s="28" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
@@ -12034,7 +13494,7 @@
         </is>
       </c>
       <c r="C36" s="41" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D36" s="42" t="inlineStr">
         <is>
@@ -12052,7 +13512,7 @@
         </is>
       </c>
       <c r="G36" s="44" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H36" s="45" t="inlineStr">
         <is>
@@ -12082,7 +13542,7 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
@@ -12100,7 +13560,7 @@
         </is>
       </c>
       <c r="G37" s="28" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
@@ -12130,7 +13590,7 @@
         </is>
       </c>
       <c r="C38" s="41" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D38" s="42" t="inlineStr">
         <is>
@@ -12148,7 +13608,7 @@
         </is>
       </c>
       <c r="G38" s="44" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H38" s="45" t="inlineStr">
         <is>
@@ -12178,7 +13638,7 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
@@ -12196,7 +13656,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
@@ -12226,7 +13686,7 @@
         </is>
       </c>
       <c r="C40" s="41" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D40" s="42" t="inlineStr">
         <is>
@@ -12244,7 +13704,7 @@
         </is>
       </c>
       <c r="G40" s="44" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="H40" s="45" t="inlineStr">
         <is>
@@ -12274,7 +13734,7 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
@@ -12292,7 +13752,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
@@ -12322,7 +13782,7 @@
         </is>
       </c>
       <c r="C42" s="41" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="D42" s="42" t="inlineStr">
         <is>
@@ -12340,7 +13800,7 @@
         </is>
       </c>
       <c r="G42" s="44" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H42" s="45" t="inlineStr">
         <is>
@@ -12370,7 +13830,7 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="D43" s="26" t="inlineStr">
         <is>
@@ -12388,7 +13848,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
@@ -12397,7 +13857,7 @@
       </c>
       <c r="I43" s="59" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (DRB102 56)</t>
+          <t>EHPS relay coil (-) (DRB102 85)</t>
         </is>
       </c>
       <c r="J43" s="60" t="inlineStr">

--- a/docs/harness/wirelist/A-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/A-engine-wirelist.xlsx
@@ -1536,14 +1536,10 @@
       </c>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W6" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W6" s="50" t="inlineStr"/>
       <c r="X6" s="50" t="inlineStr">
         <is>
           <t>Yellow-White</t>
@@ -1767,11 +1763,7 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="W8" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W8" s="50" t="inlineStr"/>
       <c r="X8" s="50" t="inlineStr">
         <is>
           <t>Yellow-Blue-Yellow</t>
@@ -1994,14 +1986,10 @@
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W10" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W10" s="50" t="inlineStr"/>
       <c r="X10" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow</t>
@@ -3374,14 +3362,10 @@
       </c>
       <c r="V22" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W22" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W22" s="50" t="inlineStr"/>
       <c r="X22" s="50" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
@@ -3713,14 +3697,10 @@
       </c>
       <c r="V25" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W25" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W25" s="34" t="inlineStr"/>
       <c r="X25" s="34" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
@@ -3937,7 +3917,7 @@
       </c>
       <c r="V27" s="34" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W27" s="34" t="inlineStr"/>
@@ -4048,7 +4028,7 @@
       </c>
       <c r="V28" s="50" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W28" s="50" t="inlineStr"/>
@@ -4159,7 +4139,7 @@
       </c>
       <c r="V29" s="34" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W29" s="34" t="inlineStr"/>
@@ -4270,7 +4250,7 @@
       </c>
       <c r="V30" s="50" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W30" s="50" t="inlineStr"/>
@@ -4381,7 +4361,7 @@
       </c>
       <c r="V31" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W31" s="34" t="inlineStr"/>
@@ -4492,7 +4472,7 @@
       </c>
       <c r="V32" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W32" s="50" t="inlineStr"/>
@@ -4603,7 +4583,7 @@
       </c>
       <c r="V33" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W33" s="34" t="inlineStr"/>
@@ -4714,7 +4694,7 @@
       </c>
       <c r="V34" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W34" s="50" t="inlineStr"/>
@@ -4825,7 +4805,7 @@
       </c>
       <c r="V35" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W35" s="34" t="inlineStr"/>
@@ -4936,7 +4916,7 @@
       </c>
       <c r="V36" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W36" s="50" t="inlineStr"/>
@@ -5047,7 +5027,7 @@
       </c>
       <c r="V37" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W37" s="34" t="inlineStr"/>
@@ -6855,14 +6835,10 @@
       </c>
       <c r="V53" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W53" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W53" s="34" t="inlineStr"/>
       <c r="X53" s="34" t="inlineStr">
         <is>
           <t>Blue-Yellow-White</t>
@@ -7319,14 +7295,10 @@
       </c>
       <c r="V57" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W57" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W57" s="34" t="inlineStr"/>
       <c r="X57" s="34" t="inlineStr">
         <is>
           <t>Blue-White-White</t>
@@ -7995,14 +7967,10 @@
       </c>
       <c r="V63" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W63" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W63" s="34" t="inlineStr"/>
       <c r="X63" s="34" t="inlineStr">
         <is>
           <t>White-White</t>
